--- a/data/Pet.xlsx
+++ b/data/Pet.xlsx
@@ -580,10 +580,10 @@
         <v>400</v>
       </c>
       <c r="I6" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="K6" t="n">
         <v>8000</v>
@@ -652,10 +652,10 @@
         <v>700</v>
       </c>
       <c r="I7" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="K7" t="n">
         <v>11000</v>
@@ -724,10 +724,10 @@
         <v>550</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="K8" t="n">
         <v>9000</v>
@@ -796,10 +796,10 @@
         <v>450</v>
       </c>
       <c r="I9" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="K9" t="n">
         <v>8000</v>
